--- a/Talepler/Paperwork_AI_RulePack_Template_v1.xlsx
+++ b/Talepler/Paperwork_AI_RulePack_Template_v1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vande\Desktop\Humanis\Talepler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vande\Desktop\Tasarım_Kontrol\Talepler\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970516D5-CFBE-47B6-8538-0A4D393FC8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -18,7 +18,7 @@
     <sheet name="Sonuç_Audit" sheetId="3" r:id="rId3"/>
     <sheet name="Workflow" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
